--- a/test/excel/xlsx/roundtrip/hidden.xlsx
+++ b/test/excel/xlsx/roundtrip/hidden.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-47250/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-2614/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B13CE2BA-79D4-E24B-B0B5-32ACAF8474F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0DDBADE-F7C0-0048-A398-3F84ED43D763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,10 +488,10 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
